--- a/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor</t>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 48,68</t>
+          <t>4,01; 48,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 46,34</t>
+          <t>5,47; 47,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 38,0</t>
+          <t>10,15; 38,05</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,35; 44,31</t>
+          <t>17,31; 44,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,97; 39,91</t>
+          <t>24,95; 40,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 38,38</t>
+          <t>22,18; 38,51</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,59; 46,3</t>
+          <t>21,68; 46,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,89; 48,6</t>
+          <t>23,36; 48,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 44,22</t>
+          <t>25,74; 43,8</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 40,24</t>
+          <t>18,84; 40,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 39,1</t>
+          <t>26,39; 39,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 36,15</t>
+          <t>23,81; 36,94</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3470</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6748</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>611; 7381</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>856; 7399</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3135; 11757</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>39635</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77896</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21206; 54552</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29948; 48209</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53775; 93392</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14091</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16838</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30930</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9028; 19241</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10984; 22974</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22819; 38833</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>115574</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33793; 72844</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>48224; 71335</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>86219; 133730</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 48,47</t>
+          <t>3,91; 47,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 47,23</t>
+          <t>6,98; 47,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 38,05</t>
+          <t>10,03; 39,8</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,31; 44,54</t>
+          <t>16,71; 44,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 40,17</t>
+          <t>24,66; 40,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,18; 38,51</t>
+          <t>21,6; 38,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,68; 46,21</t>
+          <t>22,84; 47,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,36; 48,86</t>
+          <t>24,01; 50,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 43,8</t>
+          <t>26,51; 44,77</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 40,62</t>
+          <t>19,91; 40,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,39; 39,04</t>
+          <t>26,16; 38,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,94</t>
+          <t>24,88; 37,03</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>611; 7381</t>
+          <t>595; 7279</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>856; 7399</t>
+          <t>1093; 7460</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3135; 11757</t>
+          <t>3100; 12298</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21206; 54552</t>
+          <t>20462; 54942</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29948; 48209</t>
+          <t>29593; 48253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53775; 93392</t>
+          <t>52383; 94033</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9028; 19241</t>
+          <t>9510; 19915</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10984; 22974</t>
+          <t>11291; 23662</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22819; 38833</t>
+          <t>23500; 39696</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33793; 72844</t>
+          <t>35717; 73114</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48224; 71335</t>
+          <t>47794; 69961</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86219; 133730</t>
+          <t>90094; 134078</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 47,8</t>
+          <t>7,36; 49,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 47,61</t>
+          <t>13,18; 57,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 39,8</t>
+          <t>12,81; 43,41</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 44,86</t>
+          <t>24,44; 40,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,66; 40,2</t>
+          <t>33,53; 49,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,6; 38,78</t>
+          <t>31,17; 42,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,84; 47,83</t>
+          <t>22,65; 48,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,01; 50,33</t>
+          <t>20,68; 45,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,51; 44,77</t>
+          <t>26,47; 43,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,91; 40,77</t>
+          <t>25,79; 38,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 38,29</t>
+          <t>32,78; 45,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,88; 37,03</t>
+          <t>30,14; 39,27</t>
         </is>
       </c>
     </row>
@@ -774,18 +774,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6322</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>595; 7279</t>
+          <t>1025; 6929</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1093; 7460</t>
+          <t>1289; 5633</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3100; 12298</t>
+          <t>3035; 10288</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>61</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>33978</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77896</t>
+          <t>73638</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20462; 54942</t>
+          <t>26370; 43241</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29593; 48253</t>
+          <t>31633; 47131</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52383; 94033</t>
+          <t>63040; 86178</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>29096</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9510; 19915</t>
+          <t>9887; 21332</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11291; 23662</t>
+          <t>8379; 18380</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23500; 39696</t>
+          <t>22284; 36785</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35717; 73114</t>
+          <t>42683; 63754</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47794; 69961</t>
+          <t>47419; 66158</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90094; 134078</t>
+          <t>93456; 121778</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,36; 49,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,18; 57,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,81; 43,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>42,04%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>24,44; 40,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33,53; 49,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31,17; 42,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>22,65; 48,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>20,68; 45,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>26,47; 43,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>25,79; 38,53</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32,78; 45,74</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30,14; 39,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2374755096144171</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3083487684350376</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2667227621712045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6322</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.07362452674710737</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1318018753719902</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1280538978513402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1025; 6929</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1289; 5633</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3035; 10288</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4977754622650082</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5758850523574544</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4340602231757959</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3148678667175239</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4204252939762901</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3641029339622034</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33978</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39660</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73638</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2443678073405652</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3353331953801342</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.3117017929138464</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>26370; 43241</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31633; 47131</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63040; 86178</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4007048470410905</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4996209069651324</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4261057761100412</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3566875979922767</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3338006518952175</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.34566817104216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15568</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13528</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29096</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.226519556238459</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2067557994487202</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2647399578979437</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9887; 21332</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8379; 18380</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22284; 36785</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4887438244933952</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4535230166483621</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4370159750833789</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3193876990993028</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3885750505526774</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3516569265573155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>52852</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>56204</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>109056</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.2579387873970066</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3278366154360199</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.301353385107934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>42683; 63754</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>47419; 66158</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>93456; 121778</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3852719095209731</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4573913188523958</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3926786971843211</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3306</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3016</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6322</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1289</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6929</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5633</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10288</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>33978</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>39660</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>73638</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>26370</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>31633</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>63040</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>43241</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>47131</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>86178</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>15568</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>13528</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>29096</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>9887</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>8379</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>22284</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>21332</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>18380</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>36785</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>52852</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>56204</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>109056</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>42683</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>47419</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>93456</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>63754</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>66158</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>121778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>